--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.64256</v>
+        <v>16.81847</v>
       </c>
       <c r="D2" t="n">
-        <v>16.37245</v>
+        <v>16.13121</v>
       </c>
       <c r="E2" t="n">
-        <v>16.39138</v>
+        <v>16.67951</v>
       </c>
       <c r="F2" t="n">
-        <v>41.59398</v>
+        <v>41.73095</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05112</v>
+        <v>0.04969</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7911</v>
+        <v>1.83758</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.84236</v>
+        <v>17.0283</v>
       </c>
       <c r="D3" t="n">
-        <v>16.45293</v>
+        <v>16.21194</v>
       </c>
       <c r="E3" t="n">
-        <v>16.31939</v>
+        <v>16.72865</v>
       </c>
       <c r="F3" t="n">
-        <v>43.30795</v>
+        <v>42.4862</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04915</v>
+        <v>0.05127</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83096</v>
+        <v>1.77336</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.54092</v>
+        <v>16.83979</v>
       </c>
       <c r="D4" t="n">
-        <v>16.50203</v>
+        <v>16.08981</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73779</v>
+        <v>16.69292</v>
       </c>
       <c r="F4" t="n">
-        <v>42.14087</v>
+        <v>42.12269</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05026</v>
+        <v>0.0498</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83424</v>
+        <v>1.78845</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.80841</v>
+        <v>16.29991</v>
       </c>
       <c r="D5" t="n">
-        <v>16.31563</v>
+        <v>16.26481</v>
       </c>
       <c r="E5" t="n">
-        <v>16.80035</v>
+        <v>16.29278</v>
       </c>
       <c r="F5" t="n">
-        <v>42.28354</v>
+        <v>42.37716</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05103</v>
+        <v>0.05016</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80173</v>
+        <v>1.80456</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.9505</v>
+        <v>16.67653</v>
       </c>
       <c r="D6" t="n">
-        <v>16.60409</v>
+        <v>16.24605</v>
       </c>
       <c r="E6" t="n">
-        <v>16.52494</v>
+        <v>16.60727</v>
       </c>
       <c r="F6" t="n">
-        <v>42.25664</v>
+        <v>42.32504</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04992</v>
+        <v>0.05083</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82942</v>
+        <v>1.82938</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.51453</v>
+        <v>16.9159</v>
       </c>
       <c r="D7" t="n">
-        <v>16.30986</v>
+        <v>16.48724</v>
       </c>
       <c r="E7" t="n">
-        <v>16.54264</v>
+        <v>16.59826</v>
       </c>
       <c r="F7" t="n">
-        <v>42.1518</v>
+        <v>42.62469</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05056</v>
+        <v>0.05054</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81904</v>
+        <v>1.8236</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.8393</v>
+        <v>16.94831</v>
       </c>
       <c r="D8" t="n">
-        <v>16.57545</v>
+        <v>16.7424</v>
       </c>
       <c r="E8" t="n">
-        <v>16.91785</v>
+        <v>16.84351</v>
       </c>
       <c r="F8" t="n">
-        <v>42.72053</v>
+        <v>42.09801</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05067</v>
+        <v>0.05094</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80716</v>
+        <v>1.79779</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.83662</v>
+        <v>16.58524</v>
       </c>
       <c r="D9" t="n">
-        <v>16.38964</v>
+        <v>16.3501</v>
       </c>
       <c r="E9" t="n">
-        <v>16.49038</v>
+        <v>16.47667</v>
       </c>
       <c r="F9" t="n">
-        <v>42.54934</v>
+        <v>42.38439</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04911</v>
+        <v>0.04963</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81705</v>
+        <v>1.84282</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.76111</v>
+        <v>16.69631</v>
       </c>
       <c r="D10" t="n">
-        <v>16.61395</v>
+        <v>16.45137</v>
       </c>
       <c r="E10" t="n">
-        <v>16.60719</v>
+        <v>16.52415</v>
       </c>
       <c r="F10" t="n">
-        <v>41.90918</v>
+        <v>42.86426</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04986</v>
+        <v>0.05126</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83398</v>
+        <v>1.79921</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.59776</v>
+        <v>16.78519</v>
       </c>
       <c r="D12" t="n">
-        <v>16.65931</v>
+        <v>16.48786</v>
       </c>
       <c r="E12" t="n">
-        <v>16.94985</v>
+        <v>16.76368</v>
       </c>
       <c r="F12" t="n">
-        <v>42.2564</v>
+        <v>42.21913</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05101</v>
+        <v>0.05083</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81832</v>
+        <v>1.79081</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.53364</v>
+        <v>17.04891</v>
       </c>
       <c r="D13" t="n">
-        <v>16.18271</v>
+        <v>16.2221</v>
       </c>
       <c r="E13" t="n">
-        <v>16.81783</v>
+        <v>16.39803</v>
       </c>
       <c r="F13" t="n">
-        <v>42.26681</v>
+        <v>42.50169</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05081</v>
+        <v>0.05035</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83518</v>
+        <v>1.80861</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.91085</v>
+        <v>16.85328</v>
       </c>
       <c r="D14" t="n">
-        <v>16.24419</v>
+        <v>16.51079</v>
       </c>
       <c r="E14" t="n">
-        <v>16.65495</v>
+        <v>16.6045</v>
       </c>
       <c r="F14" t="n">
-        <v>42.24664</v>
+        <v>43.35373</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05011</v>
+        <v>0.05045</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81474</v>
+        <v>1.80881</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.92654</v>
+        <v>16.80978</v>
       </c>
       <c r="D15" t="n">
-        <v>16.53482</v>
+        <v>16.27664</v>
       </c>
       <c r="E15" t="n">
-        <v>17.07253</v>
+        <v>16.62771</v>
       </c>
       <c r="F15" t="n">
-        <v>41.98286</v>
+        <v>41.7872</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04898</v>
+        <v>0.05075</v>
       </c>
       <c r="H15" t="n">
-        <v>1.85889</v>
+        <v>1.8316</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.87614</v>
+        <v>16.92711</v>
       </c>
       <c r="D16" t="n">
-        <v>16.70676</v>
+        <v>16.8837</v>
       </c>
       <c r="E16" t="n">
-        <v>16.74449</v>
+        <v>16.91859</v>
       </c>
       <c r="F16" t="n">
-        <v>42.91845</v>
+        <v>42.05024</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05138</v>
+        <v>0.05091</v>
       </c>
       <c r="H16" t="n">
-        <v>1.80886</v>
+        <v>1.79373</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.87009</v>
+        <v>16.78544</v>
       </c>
       <c r="D17" t="n">
-        <v>16.62221</v>
+        <v>16.41028</v>
       </c>
       <c r="E17" t="n">
-        <v>16.74101</v>
+        <v>16.72304</v>
       </c>
       <c r="F17" t="n">
-        <v>42.095</v>
+        <v>42.42498</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05092</v>
+        <v>0.04935</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7988</v>
+        <v>1.82588</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.43017</v>
+        <v>16.63972</v>
       </c>
       <c r="D18" t="n">
-        <v>16.19479</v>
+        <v>16.47256</v>
       </c>
       <c r="E18" t="n">
-        <v>16.68523</v>
+        <v>16.52893</v>
       </c>
       <c r="F18" t="n">
-        <v>42.82925</v>
+        <v>43.19392</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05036</v>
+        <v>0.04986</v>
       </c>
       <c r="H18" t="n">
-        <v>1.81502</v>
+        <v>1.82904</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.76187</v>
+        <v>16.83753</v>
       </c>
       <c r="D19" t="n">
-        <v>16.29339</v>
+        <v>16.52907</v>
       </c>
       <c r="E19" t="n">
-        <v>16.84683</v>
+        <v>16.70189</v>
       </c>
       <c r="F19" t="n">
-        <v>42.43056</v>
+        <v>42.01314</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05134</v>
+        <v>0.04996</v>
       </c>
       <c r="H19" t="n">
-        <v>1.84212</v>
+        <v>1.76587</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.8068</v>
+        <v>16.76834</v>
       </c>
       <c r="D20" t="n">
-        <v>16.5978</v>
+        <v>16.28973</v>
       </c>
       <c r="E20" t="n">
-        <v>16.35796</v>
+        <v>16.62225</v>
       </c>
       <c r="F20" t="n">
-        <v>42.1965</v>
+        <v>41.43048</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05137</v>
+        <v>0.05109</v>
       </c>
       <c r="H20" t="n">
-        <v>1.80857</v>
+        <v>1.83204</v>
       </c>
     </row>
     <row r="21">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.61367</v>
+        <v>15.64139</v>
       </c>
       <c r="D22" t="n">
-        <v>15.49894</v>
+        <v>15.4638</v>
       </c>
       <c r="E22" t="n">
-        <v>15.62806</v>
+        <v>15.55278</v>
       </c>
       <c r="F22" t="n">
-        <v>254.8727</v>
+        <v>248.96562</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.7924</v>
+        <v>15.86772</v>
       </c>
       <c r="D23" t="n">
-        <v>15.42371</v>
+        <v>15.27055</v>
       </c>
       <c r="E23" t="n">
-        <v>15.27221</v>
+        <v>15.78416</v>
       </c>
       <c r="F23" t="n">
-        <v>256.10299</v>
+        <v>247.95953</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.64052</v>
+        <v>15.7251</v>
       </c>
       <c r="D24" t="n">
-        <v>15.81993</v>
+        <v>15.50653</v>
       </c>
       <c r="E24" t="n">
-        <v>15.41444</v>
+        <v>15.54251</v>
       </c>
       <c r="F24" t="n">
-        <v>251.51666</v>
+        <v>258.80943</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.59495</v>
+        <v>15.78057</v>
       </c>
       <c r="D25" t="n">
-        <v>15.38009</v>
+        <v>15.3249</v>
       </c>
       <c r="E25" t="n">
-        <v>15.52208</v>
+        <v>15.62206</v>
       </c>
       <c r="F25" t="n">
-        <v>254.63076</v>
+        <v>258.44566</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.80041</v>
+        <v>15.56032</v>
       </c>
       <c r="D26" t="n">
-        <v>15.47874</v>
+        <v>15.27058</v>
       </c>
       <c r="E26" t="n">
-        <v>15.67361</v>
+        <v>15.52939</v>
       </c>
       <c r="F26" t="n">
-        <v>252.99044</v>
+        <v>253.53403</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.64544</v>
+        <v>15.72328</v>
       </c>
       <c r="D27" t="n">
-        <v>15.30941</v>
+        <v>15.56505</v>
       </c>
       <c r="E27" t="n">
-        <v>15.51627</v>
+        <v>15.5873</v>
       </c>
       <c r="F27" t="n">
-        <v>251.17588</v>
+        <v>253.10618</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.83773</v>
+        <v>15.41937</v>
       </c>
       <c r="D28" t="n">
-        <v>15.59214</v>
+        <v>14.94973</v>
       </c>
       <c r="E28" t="n">
-        <v>15.44233</v>
+        <v>15.3155</v>
       </c>
       <c r="F28" t="n">
-        <v>251.53864</v>
+        <v>249.20502</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.86447</v>
+        <v>15.79849</v>
       </c>
       <c r="D29" t="n">
-        <v>15.23099</v>
+        <v>15.63048</v>
       </c>
       <c r="E29" t="n">
-        <v>15.60005</v>
+        <v>15.69425</v>
       </c>
       <c r="F29" t="n">
-        <v>252.1195</v>
+        <v>250.75848</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.3443</v>
+        <v>15.7375</v>
       </c>
       <c r="D30" t="n">
-        <v>15.68747</v>
+        <v>15.30573</v>
       </c>
       <c r="E30" t="n">
-        <v>15.02966</v>
+        <v>15.70677</v>
       </c>
       <c r="F30" t="n">
-        <v>251.56474</v>
+        <v>250.1504</v>
       </c>
     </row>
     <row r="31">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.62285</v>
+        <v>16.57812</v>
       </c>
       <c r="D32" t="n">
-        <v>15.78314</v>
+        <v>15.81013</v>
       </c>
       <c r="E32" t="n">
-        <v>16.04271</v>
+        <v>16.52395</v>
       </c>
       <c r="F32" t="n">
-        <v>21.73612</v>
+        <v>21.32266</v>
       </c>
       <c r="G32" t="n">
-        <v>34.41396</v>
+        <v>33.7557</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.85611</v>
+        <v>16.86078</v>
       </c>
       <c r="D33" t="n">
-        <v>15.77197</v>
+        <v>16.03545</v>
       </c>
       <c r="E33" t="n">
-        <v>16.17284</v>
+        <v>16.33224</v>
       </c>
       <c r="F33" t="n">
-        <v>22.07957</v>
+        <v>21.50096</v>
       </c>
       <c r="G33" t="n">
-        <v>34.7281</v>
+        <v>33.58027</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.4659</v>
+        <v>16.21821</v>
       </c>
       <c r="D34" t="n">
-        <v>15.88956</v>
+        <v>15.91635</v>
       </c>
       <c r="E34" t="n">
-        <v>16.5295</v>
+        <v>15.99758</v>
       </c>
       <c r="F34" t="n">
-        <v>21.67597</v>
+        <v>21.50303</v>
       </c>
       <c r="G34" t="n">
-        <v>33.89031</v>
+        <v>33.3781</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.3683</v>
+        <v>16.64694</v>
       </c>
       <c r="D35" t="n">
-        <v>15.8042</v>
+        <v>15.90005</v>
       </c>
       <c r="E35" t="n">
-        <v>16.49593</v>
+        <v>16.31955</v>
       </c>
       <c r="F35" t="n">
-        <v>21.44594</v>
+        <v>21.35986</v>
       </c>
       <c r="G35" t="n">
-        <v>34.58777</v>
+        <v>33.85507</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.39613</v>
+        <v>16.7344</v>
       </c>
       <c r="D36" t="n">
-        <v>15.82378</v>
+        <v>15.78535</v>
       </c>
       <c r="E36" t="n">
-        <v>16.26493</v>
+        <v>16.47322</v>
       </c>
       <c r="F36" t="n">
-        <v>21.36188</v>
+        <v>21.25105</v>
       </c>
       <c r="G36" t="n">
-        <v>34.48435</v>
+        <v>33.61316</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.79084</v>
+        <v>16.67264</v>
       </c>
       <c r="D37" t="n">
-        <v>15.84094</v>
+        <v>15.69235</v>
       </c>
       <c r="E37" t="n">
-        <v>16.19468</v>
+        <v>16.22518</v>
       </c>
       <c r="F37" t="n">
-        <v>21.28921</v>
+        <v>21.14575</v>
       </c>
       <c r="G37" t="n">
-        <v>34.0143</v>
+        <v>34.51051</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.57923</v>
+        <v>16.86401</v>
       </c>
       <c r="D38" t="n">
-        <v>15.82295</v>
+        <v>16.04476</v>
       </c>
       <c r="E38" t="n">
-        <v>16.56488</v>
+        <v>16.04681</v>
       </c>
       <c r="F38" t="n">
-        <v>21.71671</v>
+        <v>21.59197</v>
       </c>
       <c r="G38" t="n">
-        <v>34.63337</v>
+        <v>34.36605</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.93754</v>
+        <v>16.60006</v>
       </c>
       <c r="D39" t="n">
-        <v>15.98917</v>
+        <v>15.92562</v>
       </c>
       <c r="E39" t="n">
-        <v>16.40614</v>
+        <v>16.34566</v>
       </c>
       <c r="F39" t="n">
-        <v>21.63546</v>
+        <v>21.83827</v>
       </c>
       <c r="G39" t="n">
-        <v>34.03798</v>
+        <v>33.94404</v>
       </c>
     </row>
     <row r="40">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.84506</v>
+        <v>16.72894</v>
       </c>
       <c r="D40" t="n">
-        <v>15.6609</v>
+        <v>16.2469</v>
       </c>
       <c r="E40" t="n">
-        <v>16.3737</v>
+        <v>16.42917</v>
       </c>
       <c r="F40" t="n">
-        <v>21.247</v>
+        <v>21.48562</v>
       </c>
       <c r="G40" t="n">
-        <v>34.48787</v>
+        <v>34.57532</v>
       </c>
     </row>
     <row r="41">
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16.49821</v>
+        <v>16.71071</v>
       </c>
       <c r="D42" t="n">
-        <v>15.93721</v>
+        <v>16.04374</v>
       </c>
       <c r="E42" t="n">
-        <v>16.18736</v>
+        <v>16.3569</v>
       </c>
       <c r="F42" t="n">
-        <v>21.63877</v>
+        <v>21.96846</v>
       </c>
       <c r="G42" t="n">
-        <v>33.10894</v>
+        <v>33.62108</v>
       </c>
     </row>
     <row r="43">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.64167</v>
+        <v>16.43171</v>
       </c>
       <c r="D43" t="n">
-        <v>16.19907</v>
+        <v>16.12879</v>
       </c>
       <c r="E43" t="n">
-        <v>16.41518</v>
+        <v>16.39464</v>
       </c>
       <c r="F43" t="n">
-        <v>21.45195</v>
+        <v>21.57123</v>
       </c>
       <c r="G43" t="n">
-        <v>33.45718</v>
+        <v>34.06032</v>
       </c>
     </row>
     <row r="44">
@@ -1451,19 +1451,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.35846</v>
+        <v>16.59831</v>
       </c>
       <c r="D44" t="n">
-        <v>16.03764</v>
+        <v>15.71145</v>
       </c>
       <c r="E44" t="n">
-        <v>16.28098</v>
+        <v>16.45624</v>
       </c>
       <c r="F44" t="n">
-        <v>21.42284</v>
+        <v>21.52363</v>
       </c>
       <c r="G44" t="n">
-        <v>34.05462</v>
+        <v>33.891</v>
       </c>
     </row>
     <row r="45">
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.14185</v>
+        <v>16.69097</v>
       </c>
       <c r="D45" t="n">
-        <v>15.82499</v>
+        <v>16.1128</v>
       </c>
       <c r="E45" t="n">
-        <v>16.17054</v>
+        <v>16.64754</v>
       </c>
       <c r="F45" t="n">
-        <v>21.42034</v>
+        <v>21.86949</v>
       </c>
       <c r="G45" t="n">
-        <v>34.60245</v>
+        <v>33.84549</v>
       </c>
     </row>
     <row r="46">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.39189</v>
+        <v>16.63834</v>
       </c>
       <c r="D46" t="n">
-        <v>15.71339</v>
+        <v>16.03704</v>
       </c>
       <c r="E46" t="n">
-        <v>16.3514</v>
+        <v>16.46035</v>
       </c>
       <c r="F46" t="n">
-        <v>21.9505</v>
+        <v>21.49359</v>
       </c>
       <c r="G46" t="n">
-        <v>34.09425</v>
+        <v>34.02914</v>
       </c>
     </row>
     <row r="47">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.53489</v>
+        <v>16.58196</v>
       </c>
       <c r="D47" t="n">
-        <v>16.16386</v>
+        <v>15.98307</v>
       </c>
       <c r="E47" t="n">
-        <v>16.30437</v>
+        <v>16.47872</v>
       </c>
       <c r="F47" t="n">
-        <v>21.71439</v>
+        <v>21.61526</v>
       </c>
       <c r="G47" t="n">
-        <v>33.7733</v>
+        <v>34.43547</v>
       </c>
     </row>
     <row r="48">
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.2028</v>
+        <v>16.50248</v>
       </c>
       <c r="D48" t="n">
-        <v>15.67274</v>
+        <v>15.68166</v>
       </c>
       <c r="E48" t="n">
-        <v>16.09788</v>
+        <v>16.303</v>
       </c>
       <c r="F48" t="n">
-        <v>21.83179</v>
+        <v>21.99377</v>
       </c>
       <c r="G48" t="n">
-        <v>33.64447</v>
+        <v>33.63972</v>
       </c>
     </row>
     <row r="49">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.37558</v>
+        <v>16.5753</v>
       </c>
       <c r="D49" t="n">
-        <v>16.09115</v>
+        <v>15.85044</v>
       </c>
       <c r="E49" t="n">
-        <v>16.19287</v>
+        <v>16.25415</v>
       </c>
       <c r="F49" t="n">
-        <v>21.61726</v>
+        <v>21.47248</v>
       </c>
       <c r="G49" t="n">
-        <v>33.6808</v>
+        <v>34.07376</v>
       </c>
     </row>
     <row r="50">
@@ -1583,19 +1583,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16.71055</v>
+        <v>16.58447</v>
       </c>
       <c r="D50" t="n">
-        <v>16.0526</v>
+        <v>15.48157</v>
       </c>
       <c r="E50" t="n">
-        <v>16.033</v>
+        <v>16.02273</v>
       </c>
       <c r="F50" t="n">
-        <v>21.60181</v>
+        <v>21.59602</v>
       </c>
       <c r="G50" t="n">
-        <v>34.35576</v>
+        <v>33.87116</v>
       </c>
     </row>
     <row r="51">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.60562</v>
+        <v>0.60463</v>
       </c>
       <c r="D52" t="n">
-        <v>1.0935</v>
+        <v>1.09587</v>
       </c>
     </row>
     <row r="53">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.59772</v>
+        <v>0.60072</v>
       </c>
       <c r="D53" t="n">
-        <v>1.09539</v>
+        <v>1.10952</v>
       </c>
     </row>
     <row r="54">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.60733</v>
+        <v>0.60959</v>
       </c>
       <c r="D54" t="n">
-        <v>1.08392</v>
+        <v>1.11519</v>
       </c>
     </row>
     <row r="55">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.5980799999999999</v>
+        <v>0.5966399999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>1.0936</v>
+        <v>1.08114</v>
       </c>
     </row>
     <row r="56">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.60077</v>
+        <v>0.60558</v>
       </c>
       <c r="D56" t="n">
-        <v>1.09775</v>
+        <v>1.10282</v>
       </c>
     </row>
     <row r="57">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.58251</v>
+        <v>0.59899</v>
       </c>
       <c r="D57" t="n">
-        <v>1.10614</v>
+        <v>1.09276</v>
       </c>
     </row>
     <row r="58">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.59985</v>
+        <v>0.5942</v>
       </c>
       <c r="D58" t="n">
-        <v>1.09343</v>
+        <v>1.12454</v>
       </c>
     </row>
     <row r="59">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.59921</v>
+        <v>0.5970299999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>1.1047</v>
+        <v>1.11606</v>
       </c>
     </row>
     <row r="60">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.60571</v>
+        <v>0.60194</v>
       </c>
       <c r="D60" t="n">
-        <v>1.11103</v>
+        <v>1.08796</v>
       </c>
     </row>
     <row r="61">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.59666</v>
+        <v>0.61868</v>
       </c>
       <c r="D62" t="n">
-        <v>1.10142</v>
+        <v>1.08127</v>
       </c>
     </row>
     <row r="63">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.59817</v>
+        <v>0.61032</v>
       </c>
       <c r="D63" t="n">
-        <v>1.10117</v>
+        <v>1.09609</v>
       </c>
     </row>
     <row r="64">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.61933</v>
+        <v>0.60373</v>
       </c>
       <c r="D64" t="n">
-        <v>1.10463</v>
+        <v>1.11585</v>
       </c>
     </row>
     <row r="65">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.6054</v>
+        <v>0.60201</v>
       </c>
       <c r="D65" t="n">
-        <v>1.10258</v>
+        <v>1.10582</v>
       </c>
     </row>
     <row r="66">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.60904</v>
+        <v>0.61141</v>
       </c>
       <c r="D66" t="n">
-        <v>1.1441</v>
+        <v>1.11381</v>
       </c>
     </row>
     <row r="67">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.60599</v>
+        <v>0.5969100000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>1.10544</v>
+        <v>1.12002</v>
       </c>
     </row>
     <row r="68">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.59848</v>
+        <v>0.60405</v>
       </c>
       <c r="D68" t="n">
-        <v>1.11246</v>
+        <v>1.12259</v>
       </c>
     </row>
     <row r="69">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.60672</v>
+        <v>0.60058</v>
       </c>
       <c r="D69" t="n">
-        <v>1.11428</v>
+        <v>1.12323</v>
       </c>
     </row>
     <row r="70">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.60079</v>
+        <v>0.60747</v>
       </c>
       <c r="D70" t="n">
-        <v>1.12388</v>
+        <v>1.10166</v>
       </c>
     </row>
     <row r="71">
@@ -1920,28 +1920,28 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.756</v>
+        <v>0.74452</v>
       </c>
       <c r="D72" t="n">
-        <v>0.08092000000000001</v>
+        <v>0.07987</v>
       </c>
       <c r="E72" t="n">
-        <v>0.59291</v>
+        <v>0.60981</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9497100000000001</v>
+        <v>0.94511</v>
       </c>
       <c r="G72" t="n">
-        <v>0.10676</v>
+        <v>0.10741</v>
       </c>
       <c r="H72" t="n">
-        <v>0.00747</v>
+        <v>0.00752</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09193999999999999</v>
+        <v>0.09233</v>
       </c>
       <c r="J72" t="n">
-        <v>0.12631</v>
+        <v>0.1264</v>
       </c>
     </row>
     <row r="73">
@@ -1951,28 +1951,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.74438</v>
+        <v>0.74783</v>
       </c>
       <c r="D73" t="n">
-        <v>0.08008</v>
+        <v>0.08115</v>
       </c>
       <c r="E73" t="n">
-        <v>0.60748</v>
+        <v>0.60642</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9433</v>
+        <v>0.97406</v>
       </c>
       <c r="G73" t="n">
-        <v>0.10715</v>
+        <v>0.10985</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00756</v>
+        <v>0.0076</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09304999999999999</v>
+        <v>0.09236999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>0.12771</v>
+        <v>0.12678</v>
       </c>
     </row>
     <row r="74">
@@ -1982,28 +1982,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.73958</v>
+        <v>0.73953</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0796</v>
+        <v>0.07994999999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>0.59902</v>
+        <v>0.60785</v>
       </c>
       <c r="F74" t="n">
-        <v>0.95316</v>
+        <v>0.93306</v>
       </c>
       <c r="G74" t="n">
-        <v>0.11013</v>
+        <v>0.10902</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00758</v>
+        <v>0.00757</v>
       </c>
       <c r="I74" t="n">
-        <v>0.09184</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>0.12588</v>
+        <v>0.12581</v>
       </c>
     </row>
     <row r="75">
@@ -2013,28 +2013,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.75101</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>0.08094999999999999</v>
+        <v>0.07976999999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5968599999999999</v>
+        <v>0.61133</v>
       </c>
       <c r="F75" t="n">
-        <v>0.95228</v>
+        <v>0.94987</v>
       </c>
       <c r="G75" t="n">
-        <v>0.10892</v>
+        <v>0.10971</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0076</v>
+        <v>0.0077</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0936</v>
+        <v>0.09256</v>
       </c>
       <c r="J75" t="n">
-        <v>0.12502</v>
+        <v>0.12751</v>
       </c>
     </row>
     <row r="76">
@@ -2044,28 +2044,28 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.7505500000000001</v>
+        <v>0.74753</v>
       </c>
       <c r="D76" t="n">
-        <v>0.08017000000000001</v>
+        <v>0.07968</v>
       </c>
       <c r="E76" t="n">
-        <v>0.61102</v>
+        <v>0.59205</v>
       </c>
       <c r="F76" t="n">
-        <v>0.96078</v>
+        <v>0.9683</v>
       </c>
       <c r="G76" t="n">
-        <v>0.10981</v>
+        <v>0.10869</v>
       </c>
       <c r="H76" t="n">
-        <v>0.00747</v>
+        <v>0.00762</v>
       </c>
       <c r="I76" t="n">
-        <v>0.09152</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>0.127</v>
+        <v>0.12734</v>
       </c>
     </row>
     <row r="77">
@@ -2075,28 +2075,28 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.74751</v>
+        <v>0.73297</v>
       </c>
       <c r="D77" t="n">
-        <v>0.08103</v>
+        <v>0.08075</v>
       </c>
       <c r="E77" t="n">
-        <v>0.59184</v>
+        <v>0.6035199999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>0.95213</v>
+        <v>0.95203</v>
       </c>
       <c r="G77" t="n">
-        <v>0.10549</v>
+        <v>0.10888</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00746</v>
+        <v>0.00765</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09354</v>
+        <v>0.09276</v>
       </c>
       <c r="J77" t="n">
-        <v>0.12528</v>
+        <v>0.12934</v>
       </c>
     </row>
     <row r="78">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.74677</v>
+        <v>0.7397</v>
       </c>
       <c r="D78" t="n">
-        <v>0.07876</v>
+        <v>0.07837</v>
       </c>
       <c r="E78" t="n">
-        <v>0.60976</v>
+        <v>0.61963</v>
       </c>
       <c r="F78" t="n">
-        <v>0.93982</v>
+        <v>0.9658</v>
       </c>
       <c r="G78" t="n">
-        <v>0.10766</v>
+        <v>0.11002</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00754</v>
+        <v>0.00761</v>
       </c>
       <c r="I78" t="n">
-        <v>0.09107999999999999</v>
+        <v>0.09401</v>
       </c>
       <c r="J78" t="n">
-        <v>0.12622</v>
+        <v>0.12844</v>
       </c>
     </row>
     <row r="79">
@@ -2137,28 +2137,28 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.723</v>
+        <v>0.74364</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0806</v>
+        <v>0.0813</v>
       </c>
       <c r="E79" t="n">
-        <v>0.60578</v>
+        <v>0.6081299999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>0.98076</v>
+        <v>0.96388</v>
       </c>
       <c r="G79" t="n">
-        <v>0.11021</v>
+        <v>0.10824</v>
       </c>
       <c r="H79" t="n">
-        <v>0.00759</v>
+        <v>0.00764</v>
       </c>
       <c r="I79" t="n">
-        <v>0.09382</v>
+        <v>0.09193999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>0.12352</v>
+        <v>0.12372</v>
       </c>
     </row>
     <row r="80">
@@ -2168,28 +2168,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.7653</v>
+        <v>0.7307399999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>0.08166</v>
+        <v>0.0809</v>
       </c>
       <c r="E80" t="n">
-        <v>0.60812</v>
+        <v>0.61185</v>
       </c>
       <c r="F80" t="n">
-        <v>0.97416</v>
+        <v>0.95689</v>
       </c>
       <c r="G80" t="n">
-        <v>0.10594</v>
+        <v>0.1089</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00771</v>
+        <v>0.00757</v>
       </c>
       <c r="I80" t="n">
-        <v>0.09216000000000001</v>
+        <v>0.0914</v>
       </c>
       <c r="J80" t="n">
-        <v>0.12778</v>
+        <v>0.12763</v>
       </c>
     </row>
   </sheetData>
